--- a/data/meta_gerente.xlsx
+++ b/data/meta_gerente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\christian.roque\Desktop\Total_Day\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A82E085F-95E7-40C1-9C98-49ABE86E7969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E181318-08E1-4F81-85ED-333B51E602DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,15 +36,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>cod_filial</t>
   </si>
   <si>
+    <t>cod_gerente</t>
+  </si>
+  <si>
+    <t>gerente</t>
+  </si>
+  <si>
+    <t>meta gerente</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>JOSE JUSSIER GARCIA PACHECO JUNIOR</t>
   </si>
   <si>
-    <t xml:space="preserve"> GERUSIA MARIA DA SILVA</t>
+    <t>GERUSIA MARIA DA SILVA</t>
   </si>
   <si>
     <t>EDSON DA SILVA</t>
@@ -56,22 +83,13 @@
     <t>TIAGO FERNANDES</t>
   </si>
   <si>
-    <t xml:space="preserve"> WESLEY DE OLIVEIRA PAZ</t>
+    <t>WESLEY DE OLIVEIRA PAZ</t>
   </si>
   <si>
     <t>REGINALDO ALMEIDA</t>
   </si>
   <si>
     <t>GLEIDSON NOBRE</t>
-  </si>
-  <si>
-    <t>cod_gerente</t>
-  </si>
-  <si>
-    <t>gerente</t>
-  </si>
-  <si>
-    <t>meta gerente</t>
   </si>
 </sst>
 </file>
@@ -458,122 +476,122 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1">
         <v>4326288.6099999994</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>818000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>690000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1">
         <v>4936147.33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1">
-        <v>482973.27899999998</v>
+        <v>393463.95299999992</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
-        <v>1126937.6509999998</v>
+        <v>918082.5569999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>8</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1">
         <v>2051336.06</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1">
         <v>1414418.0400000003</v>
